--- a/data_modelos/Relación_impactos_variables_climáticas.xlsx
+++ b/data_modelos/Relación_impactos_variables_climáticas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\PDE\DEMO\data_modelos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC0ED987-224E-4009-9D8E-AF2EB03B7876}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{450906F1-839F-4363-8C90-D9636EEFFFF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28695" yWindow="0" windowWidth="14610" windowHeight="16305" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6510" yWindow="3015" windowWidth="21600" windowHeight="11835" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Relacion impactos-indicadoresRe" sheetId="2" r:id="rId1"/>
@@ -1446,7 +1446,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>36</v>
       </c>
@@ -1466,7 +1466,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>37</v>
       </c>
@@ -1486,7 +1486,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>38</v>
       </c>
@@ -1746,7 +1746,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="52" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>51</v>
       </c>
@@ -1754,7 +1754,7 @@
         <v>6</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>45</v>
@@ -1766,7 +1766,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="53" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>52</v>
       </c>
@@ -1774,7 +1774,7 @@
         <v>6</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>45</v>
@@ -1806,7 +1806,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="55" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>54</v>
       </c>
@@ -1814,7 +1814,7 @@
         <v>6</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>45</v>
@@ -1886,7 +1886,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="59" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>58</v>
       </c>
@@ -1894,7 +1894,7 @@
         <v>6</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>45</v>
@@ -1906,7 +1906,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="60" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>59</v>
       </c>
@@ -1914,7 +1914,7 @@
         <v>6</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>45</v>
@@ -1926,7 +1926,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="61" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>60</v>
       </c>
@@ -1934,7 +1934,7 @@
         <v>6</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>45</v>
@@ -1966,7 +1966,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="63" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>62</v>
       </c>
@@ -1974,7 +1974,7 @@
         <v>6</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>45</v>
@@ -2086,7 +2086,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="69" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>68</v>
       </c>
@@ -2094,7 +2094,7 @@
         <v>6</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D69" s="1" t="s">
         <v>45</v>
@@ -4006,7 +4006,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" s="1">
         <v>164</v>
       </c>
@@ -4368,9 +4368,31 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:F182" xr:uid="{F1B4DC7D-DF22-4273-B477-901A44468A09}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="ELO"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="2">
+      <filters>
+        <filter val="Inundación"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="3">
+      <filters>
+        <filter val="Inundación costera"/>
+      </filters>
+    </filterColumn>
     <filterColumn colId="4">
       <filters>
-        <filter val="Muelle"/>
+        <filter val="Accesos ferroviarios y terminales ferroportuarias"/>
+        <filter val="Accesos viarios"/>
+        <filter val="Alumbrado"/>
+        <filter val="Edificios de servicios generales (Oficinas, Aduanas, PIF, Control de accesos, etc.)"/>
+        <filter val="Manipulación de mercancía"/>
+        <filter val="Pavimentos"/>
+        <filter val="Superficies"/>
+        <filter val="Zonas de Actividad Logística"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/data_modelos/Relación_impactos_variables_climáticas.xlsx
+++ b/data_modelos/Relación_impactos_variables_climáticas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\PDE\DEMO\data_modelos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{450906F1-839F-4363-8C90-D9636EEFFFF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{141BE7AD-4CC0-4960-AFF2-AFC2A2DC738A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6510" yWindow="3015" windowWidth="21600" windowHeight="11835" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Relacion impactos-indicadoresRe" sheetId="2" r:id="rId1"/>
@@ -1746,7 +1746,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>51</v>
       </c>
@@ -1766,7 +1766,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>52</v>
       </c>
@@ -1806,7 +1806,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>54</v>
       </c>
@@ -1886,7 +1886,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>58</v>
       </c>
@@ -1906,7 +1906,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>59</v>
       </c>
@@ -1926,7 +1926,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>60</v>
       </c>
@@ -1986,7 +1986,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="64" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>63</v>
       </c>
@@ -2006,7 +2006,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="65" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>64</v>
       </c>
@@ -2086,7 +2086,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>68</v>
       </c>
@@ -4368,31 +4368,9 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:F182" xr:uid="{F1B4DC7D-DF22-4273-B477-901A44468A09}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="ELO"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="2">
-      <filters>
-        <filter val="Inundación"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="3">
-      <filters>
-        <filter val="Inundación costera"/>
-      </filters>
-    </filterColumn>
     <filterColumn colId="4">
       <filters>
-        <filter val="Accesos ferroviarios y terminales ferroportuarias"/>
-        <filter val="Accesos viarios"/>
-        <filter val="Alumbrado"/>
-        <filter val="Edificios de servicios generales (Oficinas, Aduanas, PIF, Control de accesos, etc.)"/>
         <filter val="Manipulación de mercancía"/>
-        <filter val="Pavimentos"/>
-        <filter val="Superficies"/>
-        <filter val="Zonas de Actividad Logística"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/data_modelos/Relación_impactos_variables_climáticas.xlsx
+++ b/data_modelos/Relación_impactos_variables_climáticas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\PDE\DEMO\data_modelos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{141BE7AD-4CC0-4960-AFF2-AFC2A2DC738A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A21A8109-9E45-4EA3-AABC-DFBAE9127121}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1966,7 +1966,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>62</v>
       </c>
@@ -1986,7 +1986,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>63</v>
       </c>
@@ -2006,7 +2006,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>64</v>
       </c>
@@ -2026,7 +2026,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="66" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>65</v>
       </c>
@@ -2046,7 +2046,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="67" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>66</v>
       </c>
@@ -2066,7 +2066,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="68" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>67</v>
       </c>
@@ -4370,7 +4370,7 @@
   <autoFilter ref="A1:F182" xr:uid="{F1B4DC7D-DF22-4273-B477-901A44468A09}">
     <filterColumn colId="4">
       <filters>
-        <filter val="Manipulación de mercancía"/>
+        <filter val="Personal del puerto"/>
       </filters>
     </filterColumn>
   </autoFilter>
